--- a/exports/complaint_report.xlsx
+++ b/exports/complaint_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,8 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -455,26 +463,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMP006</t>
+          <t>CMP001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AST006</t>
+          <t>AST001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Laptop battery is not working properly</t>
+          <t>Laptop is not starting</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46272</v>
+        <v>46204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -485,150 +493,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CMP005</t>
+          <t>CMP002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EMP005</t>
+          <t>EMP002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AST005</t>
+          <t>AST002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Monitor screen flickering</t>
+          <t>Desktop running very slow</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CMP004</t>
+          <t>CMP003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EMP004</t>
+          <t>EMP003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AST004</t>
+          <t>AST003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Laptop battery draining fast</t>
+          <t>Printer is not printing</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMP003</t>
+          <t>CMP004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EMP003</t>
+          <t>EMP004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AST003</t>
+          <t>AST004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Printer is not printing</t>
+          <t>Laptop battery draining fast</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMP002</t>
+          <t>CMP005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EMP002</t>
+          <t>EMP005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AST002</t>
+          <t>AST005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desktop running very slow</t>
+          <t>Monitor screen flickering</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CMP001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AST001</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Laptop is not starting</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
